--- a/public/concepts/lista-conceptos-finning.xlsx
+++ b/public/concepts/lista-conceptos-finning.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB481"/>
+  <dimension ref="A1:AB485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3764,7 +3764,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>imponibleAfcLey</t>
+          <t>agrega_sis</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Imponible informado AFC ley 21.227</t>
+          <t>Agrega SIS a sueldo patronal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3899,7 +3899,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>agrega_sis</t>
+          <t>imponibleAfcLey</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Agrega SIS a sueldo patronal</t>
+          <t>Imponible informado AFC ley 21.227</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -18779,7 +18779,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>comisionMi</t>
+          <t>bonoProduccionTolva</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Comisiones MI</t>
+          <t>BONO PRODUCCION TOLVA</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18812,17 +18812,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2103 - Comisiones</t>
+          <t>2123 - Otras remuneraciones superiores a un mes</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -18919,7 +18919,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>bonoProduccionTolva</t>
+          <t>comisionMi</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BONO PRODUCCION TOLVA</t>
+          <t>Comisiones MI</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18952,17 +18952,17 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2123 - Otras remuneraciones superiores a un mes</t>
+          <t>2103 - Comisiones</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -19759,7 +19759,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>horasEx75</t>
+          <t>incentivoCollahuasi</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Horas Extras 75%</t>
+          <t>INCENTIVO COLLAHUASI</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>ine_sobretiempo</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2102 - Sobresueldo</t>
+          <t>2123 - Otras remuneraciones superiores a un mes</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -19899,7 +19899,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>incentivoCollahuasi</t>
+          <t>horasEx75</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -19909,7 +19909,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>INCENTIVO COLLAHUASI</t>
+          <t>Horas Extras 75%</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>ine_sobretiempo</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2123 - Otras remuneraciones superiores a un mes</t>
+          <t>2102 - Sobresueldo</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -19957,7 +19957,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -23384,7 +23384,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>promedioComisio5NLZG</t>
+          <t>promedioRemunerX0NS7</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PROMEDIO COMISIONES VACACIONES</t>
+          <t>PROMEDIO REMUNERACION VARIABLE</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>promedioRemunerX0NS7</t>
+          <t>promedioComisio5NLZG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PROMEDIO REMUNERACION VARIABLE</t>
+          <t>PROMEDIO COMISIONES VACACIONES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -41342,22 +41342,22 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -44629,17 +44629,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>apvc</t>
+          <t>apvUF</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3L0204</t>
+          <t>3L0201</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>APVC Ahorro voluntario colectivo</t>
+          <t>APV UF</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -44648,7 +44648,7 @@
         </is>
       </c>
       <c r="E319" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -44662,12 +44662,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>3157 - Cotización APVc Mod A</t>
+          <t>3155 - Cotización APVi Mod A</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -44722,7 +44722,7 @@
       </c>
       <c r="T319" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U319" t="inlineStr">
@@ -44769,17 +44769,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>apviConvenido</t>
+          <t>apvPESOS</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3L0210</t>
+          <t>3L0202</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>APVI Deposito Convenido</t>
+          <t>APV PESOS</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -44788,7 +44788,7 @@
         </is>
       </c>
       <c r="E320" s="3" t="n">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -44802,7 +44802,12 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>3155 - Cotización APVi Mod A</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
@@ -44857,7 +44862,7 @@
       </c>
       <c r="T320" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U320" t="inlineStr">
@@ -44904,17 +44909,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>voluntarioCoti</t>
+          <t>apvc</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3L0425</t>
+          <t>3L0204</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Afiliado Voluntario Cotizacion</t>
+          <t>APVC Ahorro voluntario colectivo</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -44923,7 +44928,7 @@
         </is>
       </c>
       <c r="E321" s="3" t="n">
-        <v>425</v>
+        <v>204</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -44942,7 +44947,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>3185 - Otros descuentos</t>
+          <t>3157 - Cotización APVc Mod A</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -45044,17 +45049,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>voluntarioAhor</t>
+          <t>apviConvenido</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3L0426</t>
+          <t>3L0210</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Afiliado Voluntario Ahorro</t>
+          <t>APVI Deposito Convenido</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -45063,7 +45068,7 @@
         </is>
       </c>
       <c r="E322" s="3" t="n">
-        <v>426</v>
+        <v>210</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -45078,11 +45083,6 @@
       <c r="H322" t="inlineStr">
         <is>
           <t>Sin Definir</t>
-        </is>
-      </c>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>3185 - Otros descuentos</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -45184,17 +45184,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>reliquidallss</t>
+          <t>voluntarioCoti</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3L0480</t>
+          <t>3L0425</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>LLSS reliquidadas</t>
+          <t>Afiliado Voluntario Cotizacion</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -45203,7 +45203,7 @@
         </is>
       </c>
       <c r="E323" s="3" t="n">
-        <v>480</v>
+        <v>425</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -45218,6 +45218,11 @@
       <c r="H323" t="inlineStr">
         <is>
           <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>3185 - Otros descuentos</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -45319,17 +45324,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>solidariohono</t>
+          <t>voluntarioAhor</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>3L0486</t>
+          <t>3L0426</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Prestamo solidario Honorario</t>
+          <t>Afiliado Voluntario Ahorro</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -45338,7 +45343,7 @@
         </is>
       </c>
       <c r="E324" s="3" t="n">
-        <v>486</v>
+        <v>426</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -45353,6 +45358,11 @@
       <c r="H324" t="inlineStr">
         <is>
           <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>3185 - Otros descuentos</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -45454,17 +45464,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>zonaExtrema</t>
+          <t>reliquidallss</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>3L0490</t>
+          <t>3L0480</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Porcentaje de Zona Extrema</t>
+          <t>LLSS reliquidadas</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -45473,7 +45483,7 @@
         </is>
       </c>
       <c r="E325" s="3" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -45497,7 +45507,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -45589,17 +45599,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>impuesto</t>
+          <t>solidariohono</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>3L0500</t>
+          <t>3L0486</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Impuesto</t>
+          <t>Prestamo solidario Honorario</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -45608,7 +45618,7 @@
         </is>
       </c>
       <c r="E326" s="3" t="n">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -45623,11 +45633,6 @@
       <c r="H326" t="inlineStr">
         <is>
           <t>Sin Definir</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>3161 - Impuesto retenido por remuneraciones</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
@@ -45729,17 +45734,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>reliquidaImpuesto</t>
+          <t>zonaExtrema</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>3L0501</t>
+          <t>3L0490</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>IMPUESTO Reliq meses anteriores</t>
+          <t>Porcentaje de Zona Extrema</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -45748,7 +45753,7 @@
         </is>
       </c>
       <c r="E327" s="3" t="n">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -45765,11 +45770,6 @@
           <t>Sin Definir</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>3164 - Impuesto retenido por reliquidación remun. devengadas otros períodos</t>
-        </is>
-      </c>
       <c r="J327" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -45777,7 +45777,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -45869,17 +45869,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>impuestoAgricola</t>
+          <t>impuesto</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3L0501</t>
+          <t>3L0500</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Impuesto Agricola</t>
+          <t>Impuesto</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -45888,7 +45888,7 @@
         </is>
       </c>
       <c r="E328" s="3" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -46009,17 +46009,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ppm</t>
+          <t>impuestoAgricola</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>3L0502</t>
+          <t>3L0501</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mayor retencion Solicitada</t>
+          <t>Impuesto Agricola</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -46028,7 +46028,7 @@
         </is>
       </c>
       <c r="E329" s="3" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>3163 - Mayor retención de impuestos solicitada por el trabajador</t>
+          <t>3161 - Impuesto retenido por remuneraciones</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -46149,17 +46149,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>imptoindMi</t>
+          <t>reliquidaImpuesto</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>3L0503</t>
+          <t>3L0501</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Impuesto retenido por ind MI</t>
+          <t>IMPUESTO Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -46168,7 +46168,7 @@
         </is>
       </c>
       <c r="E330" s="3" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -46182,17 +46182,17 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>3162 - Impuesto retenido por indemnizaciones</t>
+          <t>3164 - Impuesto retenido por reliquidación remun. devengadas otros períodos</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -46289,17 +46289,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>reliquidaTrabEmpl</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>3L0532</t>
+          <t>3L0502</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Trabajo pesado Empl Reliq anteriores</t>
+          <t>Mayor retencion Solicitada</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -46308,7 +46308,7 @@
         </is>
       </c>
       <c r="E331" s="3" t="n">
-        <v>532</v>
+        <v>502</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -46327,7 +46327,7 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ------   </t>
+          <t>3163 - Mayor retención de impuestos solicitada por el trabajador</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
@@ -46429,17 +46429,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>solidarioremu</t>
+          <t>imptoindMi</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>3L0685</t>
+          <t>3L0503</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Prestamo solidario Remuneracion</t>
+          <t>Impuesto retenido por ind MI</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -46448,7 +46448,7 @@
         </is>
       </c>
       <c r="E332" s="3" t="n">
-        <v>685</v>
+        <v>503</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -46462,17 +46462,17 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>3166 - Prestamo solidario Remuneracion</t>
+          <t>3162 - Impuesto retenido por indemnizaciones</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -46569,17 +46569,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>impuestoHonorarios</t>
+          <t>reliquidaTrabEmpl</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>3L0901</t>
+          <t>3L0532</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Retencion Honorarios</t>
+          <t>Trabajo pesado Empl Reliq anteriores</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -46588,7 +46588,7 @@
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>901</v>
+        <v>532</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -46603,6 +46603,11 @@
       <c r="H333" t="inlineStr">
         <is>
           <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ------   </t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
@@ -46704,26 +46709,26 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>sobregiro_anterior</t>
+          <t>solidarioremu</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>4D0085</t>
+          <t>3L0685</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Sobregiro mes anterior</t>
+          <t>Prestamo solidario Remuneracion</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Descuento</t>
+          <t>Descuento Legal</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
-        <v>85</v>
+        <v>685</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -46742,7 +46747,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>3185 - Otros descuentos</t>
+          <t>3166 - Prestamo solidario Remuneracion</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
@@ -46767,12 +46772,12 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
@@ -46782,7 +46787,7 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -46844,26 +46849,26 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>prestamo_sobregiro</t>
+          <t>impuestoHonorarios</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>4D0086</t>
+          <t>3L0901</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Prestamo Sobregiro</t>
+          <t>Retencion Honorarios</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Descuento</t>
+          <t>Descuento Legal</t>
         </is>
       </c>
       <c r="E335" s="3" t="n">
-        <v>86</v>
+        <v>901</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -46880,11 +46885,6 @@
           <t>Sin Definir</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>3185 - Otros descuentos</t>
-        </is>
-      </c>
       <c r="J335" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -46907,12 +46907,12 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
@@ -46922,7 +46922,7 @@
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -46984,17 +46984,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>anticipo</t>
+          <t>sobregiro_anterior</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>4D0100</t>
+          <t>4D0085</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Anticipo</t>
+          <t>Sobregiro mes anterior</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -47003,7 +47003,7 @@
         </is>
       </c>
       <c r="E336" s="3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3185 - Otros descuentos</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
@@ -47124,17 +47124,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>anticipoFingo</t>
+          <t>prestamo_sobregiro</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>4D0100</t>
+          <t>4D0086</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Anticipo Fingo</t>
+          <t>Prestamo Sobregiro</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -47143,7 +47143,7 @@
         </is>
       </c>
       <c r="E337" s="3" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3185 - Otros descuentos</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -47264,17 +47264,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>cajaCred</t>
+          <t>anticipo</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>4D0310</t>
+          <t>4D0100</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Creditos personales CCAF</t>
+          <t>Anticipo</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -47283,7 +47283,7 @@
         </is>
       </c>
       <c r="E338" s="3" t="n">
-        <v>310</v>
+        <v>100</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>3110 - Crédito social CCAF</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
@@ -47404,17 +47404,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>cajaDent</t>
+          <t>anticipoFingo</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>4D0320</t>
+          <t>4D0100</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Descuento Dental CCAF</t>
+          <t>Anticipo Fingo</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -47423,7 +47423,7 @@
         </is>
       </c>
       <c r="E339" s="3" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>3110 - Crédito social CCAF</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
@@ -47544,17 +47544,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>cajaLeas</t>
+          <t>cajaCred</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>4D0330</t>
+          <t>4D0310</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Descuentos por Leasing CCAF</t>
+          <t>Creditos personales CCAF</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -47563,7 +47563,7 @@
         </is>
       </c>
       <c r="E340" s="3" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -47684,17 +47684,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>cajaVida</t>
+          <t>cajaDent</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>4D0340</t>
+          <t>4D0320</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Descuentos por seguro de vida CCAF</t>
+          <t>Descuento Dental CCAF</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -47703,7 +47703,7 @@
         </is>
       </c>
       <c r="E341" s="3" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -47824,17 +47824,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>cajaOtro</t>
+          <t>cajaLeas</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>4D0350</t>
+          <t>4D0330</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Otros descuentos CCAF</t>
+          <t>Descuentos por Leasing CCAF</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -47843,7 +47843,7 @@
         </is>
       </c>
       <c r="E342" s="3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -47964,17 +47964,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>cajaAhor</t>
+          <t>cajaVida</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>4D0360</t>
+          <t>4D0340</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Ahorro en CCAF</t>
+          <t>Descuentos por seguro de vida CCAF</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -47983,7 +47983,7 @@
         </is>
       </c>
       <c r="E343" s="3" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -48104,17 +48104,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>cajaSegu</t>
+          <t>cajaOtro</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>4D0370</t>
+          <t>4D0350</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Seguro en CCAF</t>
+          <t>Otros descuentos CCAF</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -48123,7 +48123,7 @@
         </is>
       </c>
       <c r="E344" s="3" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -48244,17 +48244,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>finiquitoDeudas</t>
+          <t>cajaAhor</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>4D0703</t>
+          <t>4D0360</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Deuda compensada Finiquito</t>
+          <t>Ahorro en CCAF</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -48263,7 +48263,7 @@
         </is>
       </c>
       <c r="E345" s="3" t="n">
-        <v>703</v>
+        <v>360</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3110 - Crédito social CCAF</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
@@ -48384,17 +48384,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>finiquitoSeguro</t>
+          <t>cajaSegu</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>4D0704</t>
+          <t>4D0370</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Seguro Cesantia recuperado</t>
+          <t>Seguro en CCAF</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -48403,7 +48403,7 @@
         </is>
       </c>
       <c r="E346" s="3" t="n">
-        <v>704</v>
+        <v>370</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3110 - Crédito social CCAF</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
@@ -48524,17 +48524,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>finiRetencionJudiIas</t>
+          <t>finiquitoDeudas</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>4D0705</t>
+          <t>4D0703</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Retención Judicial indemnización IAS</t>
+          <t>Deuda compensada Finiquito</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -48543,7 +48543,7 @@
         </is>
       </c>
       <c r="E347" s="3" t="n">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -48664,17 +48664,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>anticipoFiniquito</t>
+          <t>finiquitoSeguro</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>4D0800</t>
+          <t>4D0704</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Anticipo de Finiquito</t>
+          <t>Seguro Cesantia recuperado</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -48683,7 +48683,7 @@
         </is>
       </c>
       <c r="E348" s="3" t="n">
-        <v>800</v>
+        <v>704</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -48804,17 +48804,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>activoDescontado</t>
+          <t>finiRetencionJudiIas</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>4D0820</t>
+          <t>4D0705</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Activos Asignados</t>
+          <t>Retención Judicial indemnización IAS</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -48823,7 +48823,7 @@
         </is>
       </c>
       <c r="E349" s="3" t="n">
-        <v>820</v>
+        <v>705</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -48944,17 +48944,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>anticipoNeto</t>
+          <t>anticipoFiniquito</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>4D1101</t>
+          <t>4D0800</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Anticipo de Liquido</t>
+          <t>Anticipo de Finiquito</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -48963,7 +48963,7 @@
         </is>
       </c>
       <c r="E350" s="3" t="n">
-        <v>1101</v>
+        <v>800</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -49084,17 +49084,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>aporteLiquidoEmK6S6F</t>
+          <t>activoDescontado</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>4D1562</t>
+          <t>4D0820</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>APORTE LIQUIDO EMPRESA ESPP</t>
+          <t>Activos Asignados</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -49103,7 +49103,7 @@
         </is>
       </c>
       <c r="E351" s="3" t="n">
-        <v>1562</v>
+        <v>820</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -49147,12 +49147,12 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -49162,7 +49162,7 @@
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -49224,17 +49224,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>cuotavivMi</t>
+          <t>anticipoNeto</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>4D2000</t>
+          <t>4D1101</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Cuota vivienda o educación MI</t>
+          <t>Anticipo de Liquido</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -49243,7 +49243,7 @@
         </is>
       </c>
       <c r="E352" s="3" t="n">
-        <v>2000</v>
+        <v>1101</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -49257,17 +49257,17 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>3181 - Cuota vivienda o educación</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -49364,17 +49364,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>credMi</t>
+          <t>aporteLiquidoEmK6S6F</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>4D2010</t>
+          <t>4D1562</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Crédito cooperativas MI</t>
+          <t>APORTE LIQUIDO EMPRESA ESPP</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -49383,7 +49383,7 @@
         </is>
       </c>
       <c r="E353" s="3" t="n">
-        <v>2010</v>
+        <v>1562</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -49402,12 +49402,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>3182 - Crédito cooperativas de ahorro</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -49427,12 +49427,12 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P353" t="inlineStr">
@@ -49442,7 +49442,7 @@
       </c>
       <c r="Q353" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -49504,17 +49504,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>otrdescMi</t>
+          <t>cuotavivMi</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>4D2020</t>
+          <t>4D2000</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Otros descuentos aut MI</t>
+          <t>Cuota vivienda o educación MI</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -49523,7 +49523,7 @@
         </is>
       </c>
       <c r="E354" s="3" t="n">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3181 - Cuota vivienda o educación</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -49644,17 +49644,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>anticipo_ccrr</t>
+          <t>credMi</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>4D2100</t>
+          <t>4D2010</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Anticipo CCRR</t>
+          <t>Crédito cooperativas MI</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -49663,7 +49663,7 @@
         </is>
       </c>
       <c r="E355" s="3" t="n">
-        <v>2100</v>
+        <v>2010</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -49672,17 +49672,22 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Cuenta Corriente</t>
+          <t>Sin categoría</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>3182 - Crédito cooperativas de ahorro</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -49712,7 +49717,7 @@
       </c>
       <c r="P355" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q355" t="inlineStr">
@@ -49779,17 +49784,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>prestamo_ccrr</t>
+          <t>otrdescMi</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>4D2200</t>
+          <t>4D2020</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Prestamo CCRR</t>
+          <t>Otros descuentos aut MI</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -49798,7 +49803,7 @@
         </is>
       </c>
       <c r="E356" s="3" t="n">
-        <v>2200</v>
+        <v>2020</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -49807,17 +49812,22 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Cuenta Corriente</t>
+          <t>Sin categoría</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -49847,7 +49857,7 @@
       </c>
       <c r="P356" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q356" t="inlineStr">
@@ -49914,17 +49924,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CuotaSindMi</t>
+          <t>anticipo_ccrr</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>4D2310</t>
+          <t>4D2100</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Cuota sindical 1 MI</t>
+          <t>Anticipo CCRR</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -49933,7 +49943,7 @@
         </is>
       </c>
       <c r="E357" s="3" t="n">
-        <v>2310</v>
+        <v>2100</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -49942,7 +49952,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Sin categoría</t>
+          <t>Cuenta Corriente</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -49950,14 +49960,9 @@
           <t>Sin Definir</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>3171 - Cuota sindical 1</t>
-        </is>
-      </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
@@ -49987,7 +49992,7 @@
       </c>
       <c r="P357" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q357" t="inlineStr">
@@ -50054,17 +50059,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>otrosDesctoMi</t>
+          <t>prestamo_ccrr</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>4D2320</t>
+          <t>4D2200</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Otros descuentos MI</t>
+          <t>Prestamo CCRR</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -50073,7 +50078,7 @@
         </is>
       </c>
       <c r="E358" s="3" t="n">
-        <v>2320</v>
+        <v>2200</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -50082,7 +50087,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Sin categoría</t>
+          <t>Cuenta Corriente</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -50090,14 +50095,9 @@
           <t>Sin Definir</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>3185 - Otros descuentos</t>
-        </is>
-      </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
@@ -50127,7 +50127,7 @@
       </c>
       <c r="P358" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q358" t="inlineStr">
@@ -50194,17 +50194,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>AnticipoPrestamoMi</t>
+          <t>CuotaSindMi</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>4D2330</t>
+          <t>4D2310</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Descuentos por anticipos y préstamos MI</t>
+          <t>Cuota sindical 1 MI</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -50213,7 +50213,7 @@
         </is>
       </c>
       <c r="E359" s="3" t="n">
-        <v>2330</v>
+        <v>2310</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3171 - Cuota sindical 1</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -50334,17 +50334,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>prestamoLeyUrgencia</t>
+          <t>otrosDesctoMi</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>4D2500</t>
+          <t>4D2320</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Prestamo ley de urgencia</t>
+          <t>Otros descuentos MI</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -50353,7 +50353,7 @@
         </is>
       </c>
       <c r="E360" s="3" t="n">
-        <v>2500</v>
+        <v>2320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -50367,17 +50367,17 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>ine_deducciones</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>3144 - Cotización voluntaria para salud</t>
+          <t>3185 - Otros descuentos</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -50474,17 +50474,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>segDeCesantiaReYYXRT</t>
+          <t>AnticipoPrestamoMi</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>4D6452</t>
+          <t>4D2330</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>SEG DE CESANTIA RELIQUIDADO</t>
+          <t>Descuentos por anticipos y préstamos MI</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -50493,7 +50493,7 @@
         </is>
       </c>
       <c r="E361" s="3" t="n">
-        <v>6452</v>
+        <v>2330</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -50507,17 +50507,17 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>3151 - Cotización AFC - trabajador</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -50537,12 +50537,12 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P361" t="inlineStr">
@@ -50552,7 +50552,7 @@
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -50614,17 +50614,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>seguroEmpresaFinning</t>
+          <t>prestamoLeyUrgencia</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>4D7101</t>
+          <t>4D2500</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>SEGURO EMPRESA FINNING</t>
+          <t>Prestamo ley de urgencia</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -50633,7 +50633,7 @@
         </is>
       </c>
       <c r="E362" s="3" t="n">
-        <v>7101</v>
+        <v>2500</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -50647,12 +50647,12 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>ine_deducciones</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3144 - Cotización voluntaria para salud</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -50677,12 +50677,12 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
@@ -50692,7 +50692,7 @@
       </c>
       <c r="Q362" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -50754,17 +50754,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>aporteBienestar2</t>
+          <t>segDeCesantiaReYYXRT</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>4D8679</t>
+          <t>4D6452</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>APORTE BIENESTAR 2</t>
+          <t>SEG DE CESANTIA RELIQUIDADO</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -50773,7 +50773,7 @@
         </is>
       </c>
       <c r="E363" s="3" t="n">
-        <v>8679</v>
+        <v>6452</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3151 - Cotización AFC - trabajador</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -50894,17 +50894,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>anticipoAguinaldo</t>
+          <t>seguroEmpresaFinning</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>4D9000</t>
+          <t>4D7101</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>ANTICIPO AGUINALDO</t>
+          <t>SEGURO EMPRESA FINNING</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -50913,7 +50913,7 @@
         </is>
       </c>
       <c r="E364" s="3" t="n">
-        <v>9000</v>
+        <v>7101</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
@@ -51034,17 +51034,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>cuotaSindicatoN2</t>
+          <t>aporteBienestar2</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>4D9000</t>
+          <t>4D8679</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO N 2</t>
+          <t>APORTE BIENESTAR 2</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -51053,7 +51053,7 @@
         </is>
       </c>
       <c r="E365" s="3" t="n">
-        <v>9000</v>
+        <v>8679</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>3172 - Cuota sindical 2</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -51174,17 +51174,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>desctoLicencias</t>
+          <t>anticipoAguinaldo</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>4D9008</t>
+          <t>4D9000</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>DESCTO LICENCIAS</t>
+          <t>ANTICIPO AGUINALDO</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -51193,7 +51193,7 @@
         </is>
       </c>
       <c r="E366" s="3" t="n">
-        <v>9008</v>
+        <v>9000</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -51314,17 +51314,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>desctoVariosBieNN9PX</t>
+          <t>cuotaSindicatoN2</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>4D9011</t>
+          <t>4D9000</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>DESCTO VARIOS BIENESTAR</t>
+          <t>CUOTA SINDICATO N 2</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -51333,7 +51333,7 @@
         </is>
       </c>
       <c r="E367" s="3" t="n">
-        <v>9011</v>
+        <v>9000</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3172 - Cuota sindical 2</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -51454,17 +51454,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>fundacionArturoLopez</t>
+          <t>desctoLicencias</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>4D9012</t>
+          <t>4D9008</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>FUNDACION ARTURO LOPEZ</t>
+          <t>DESCTO LICENCIAS</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -51473,7 +51473,7 @@
         </is>
       </c>
       <c r="E368" s="3" t="n">
-        <v>9012</v>
+        <v>9008</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -51594,17 +51594,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>prestamoEmergencia</t>
+          <t>desctoVariosBieNN9PX</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>4D9013</t>
+          <t>4D9011</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>PRESTAMO EMERGENCIA</t>
+          <t>DESCTO VARIOS BIENESTAR</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -51613,7 +51613,7 @@
         </is>
       </c>
       <c r="E369" s="3" t="n">
-        <v>9013</v>
+        <v>9011</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -51632,7 +51632,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -51734,17 +51734,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>prestamoFonasa</t>
+          <t>fundacionArturoLopez</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>4D9014</t>
+          <t>4D9012</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>PRESTAMO FONASA</t>
+          <t>FUNDACION ARTURO LOPEZ</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -51753,7 +51753,7 @@
         </is>
       </c>
       <c r="E370" s="3" t="n">
-        <v>9014</v>
+        <v>9012</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
@@ -51874,17 +51874,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>prestamoVacaciones</t>
+          <t>prestamoEmergencia</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>4D9015</t>
+          <t>4D9013</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>PRESTAMO VACACIONES</t>
+          <t>PRESTAMO EMERGENCIA</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -51893,7 +51893,7 @@
         </is>
       </c>
       <c r="E371" s="3" t="n">
-        <v>9015</v>
+        <v>9013</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -52014,17 +52014,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>seguroChilenaCoH2CAQ</t>
+          <t>prestamoFonasa</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>4D9016</t>
+          <t>4D9014</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>SEGURO CHILENA CONSOLIDADA</t>
+          <t>PRESTAMO FONASA</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -52033,7 +52033,7 @@
         </is>
       </c>
       <c r="E372" s="3" t="n">
-        <v>9016</v>
+        <v>9014</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
@@ -52154,17 +52154,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>descuentoPrestaX99SZ</t>
+          <t>prestamoVacaciones</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>4D9018</t>
+          <t>4D9015</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>DESCUENTO PRESTAMO VACACIONES</t>
+          <t>PRESTAMO VACACIONES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -52173,7 +52173,7 @@
         </is>
       </c>
       <c r="E373" s="3" t="n">
-        <v>9018</v>
+        <v>9015</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -52294,17 +52294,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>extensionTodosL3AX33</t>
+          <t>seguroChilenaCoH2CAQ</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>4D9020</t>
+          <t>4D9016</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>EXTENSION TODOS LOS SINDICATOS</t>
+          <t>SEGURO CHILENA CONSOLIDADA</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -52313,7 +52313,7 @@
         </is>
       </c>
       <c r="E374" s="3" t="n">
-        <v>9020</v>
+        <v>9016</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -52434,17 +52434,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ctaCteAnticiposRXLFJ</t>
+          <t>descuentoPrestaX99SZ</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>4D9021</t>
+          <t>4D9018</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>CTA CTE ANTICIPOS Y CARGOS VAR</t>
+          <t>DESCUENTO PRESTAMO VACACIONES</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -52453,7 +52453,7 @@
         </is>
       </c>
       <c r="E375" s="3" t="n">
-        <v>9021</v>
+        <v>9018</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -52574,17 +52574,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>comprasVariasSiZNVTG</t>
+          <t>extensionTodosL3AX33</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>4D9022</t>
+          <t>4D9020</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>COMPRAS VARIAS SINDICATO N 5</t>
+          <t>EXTENSION TODOS LOS SINDICATOS</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -52593,7 +52593,7 @@
         </is>
       </c>
       <c r="E376" s="3" t="n">
-        <v>9022</v>
+        <v>9020</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -52714,17 +52714,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>cuotaSindicatoN6</t>
+          <t>ctaCteAnticiposRXLFJ</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>4D9023</t>
+          <t>4D9021</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO N 6</t>
+          <t>CTA CTE ANTICIPOS Y CARGOS VAR</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -52733,7 +52733,7 @@
         </is>
       </c>
       <c r="E377" s="3" t="n">
-        <v>9023</v>
+        <v>9021</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>3176 - Cuota sindical 6</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
@@ -52854,17 +52854,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>comprasVariasSiZNVTH</t>
+          <t>comprasVariasSiZNVTG</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>4D9024</t>
+          <t>4D9022</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>COMPRAS VARIAS SINDICATO N 6</t>
+          <t>COMPRAS VARIAS SINDICATO N 5</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -52873,7 +52873,7 @@
         </is>
       </c>
       <c r="E378" s="3" t="n">
-        <v>9024</v>
+        <v>9022</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -52994,17 +52994,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>gastosDentalesBF0Y94</t>
+          <t>cuotaSindicatoN6</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>4D9025</t>
+          <t>4D9023</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>GASTOS DENTALES BIENESTAR</t>
+          <t>CUOTA SINDICATO N 6</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -53013,7 +53013,7 @@
         </is>
       </c>
       <c r="E379" s="3" t="n">
-        <v>9025</v>
+        <v>9023</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -53032,7 +53032,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3176 - Cuota sindical 6</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -53134,17 +53134,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>prestamoBlando</t>
+          <t>comprasVariasSiZNVTH</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>4D9026</t>
+          <t>4D9024</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>PRESTAMO BLANDO</t>
+          <t>COMPRAS VARIAS SINDICATO N 6</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -53153,7 +53153,7 @@
         </is>
       </c>
       <c r="E380" s="3" t="n">
-        <v>9026</v>
+        <v>9024</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -53274,17 +53274,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>gastosMedicosBi8QN6K</t>
+          <t>gastosDentalesBF0Y94</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>4D9027</t>
+          <t>4D9025</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>GASTOS MEDICOS BIENESTAR</t>
+          <t>GASTOS DENTALES BIENESTAR</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -53293,7 +53293,7 @@
         </is>
       </c>
       <c r="E381" s="3" t="n">
-        <v>9027</v>
+        <v>9025</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -53414,17 +53414,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>comprasSindicato1</t>
+          <t>prestamoBlando</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>4D9028</t>
+          <t>4D9026</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>COMPRAS SINDICATO 1</t>
+          <t>PRESTAMO BLANDO</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -53433,7 +53433,7 @@
         </is>
       </c>
       <c r="E382" s="3" t="n">
-        <v>9028</v>
+        <v>9026</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
@@ -53554,17 +53554,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>prestamoVivienda</t>
+          <t>gastosMedicosBi8QN6K</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>4D9029</t>
+          <t>4D9027</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>PRESTAMO VIVIENDA</t>
+          <t>GASTOS MEDICOS BIENESTAR</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -53573,7 +53573,7 @@
         </is>
       </c>
       <c r="E383" s="3" t="n">
-        <v>9029</v>
+        <v>9027</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
@@ -53694,17 +53694,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>extensionSindicatoN2</t>
+          <t>comprasSindicato1</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>4D9030</t>
+          <t>4D9028</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>EXTENSION SINDICATO N2</t>
+          <t>COMPRAS SINDICATO 1</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -53713,7 +53713,7 @@
         </is>
       </c>
       <c r="E384" s="3" t="n">
-        <v>9030</v>
+        <v>9028</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>3172 - Cuota sindical 2</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -53834,17 +53834,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>cuotaSindicatoDiperk</t>
+          <t>prestamoVivienda</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>4D9031</t>
+          <t>4D9029</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO DIPERK</t>
+          <t>PRESTAMO VIVIENDA</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -53853,7 +53853,7 @@
         </is>
       </c>
       <c r="E385" s="3" t="n">
-        <v>9031</v>
+        <v>9029</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>3171 - Cuota sindical 1</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
@@ -53974,17 +53974,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>cuotaSindicatoN1</t>
+          <t>extensionSindicatoN2</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>4D9032</t>
+          <t>4D9030</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO N 1</t>
+          <t>EXTENSION SINDICATO N2</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -53993,7 +53993,7 @@
         </is>
       </c>
       <c r="E386" s="3" t="n">
-        <v>9032</v>
+        <v>9030</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>3171 - Cuota sindical 1</t>
+          <t>3172 - Cuota sindical 2</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -54114,17 +54114,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>descuentasil</t>
+          <t>cuotaSindicatoDiperk</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>4D9033</t>
+          <t>4D9031</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Descuenta Subsidio Incapacidad Laboral</t>
+          <t>CUOTA SINDICATO DIPERK</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -54133,7 +54133,7 @@
         </is>
       </c>
       <c r="E387" s="3" t="n">
-        <v>9033</v>
+        <v>9031</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -54147,12 +54147,12 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3171 - Cuota sindical 1</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -54177,12 +54177,12 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
@@ -54192,7 +54192,7 @@
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R387" t="inlineStr">
@@ -54254,17 +54254,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>cuotaSindicatoN4</t>
+          <t>cuotaSindicatoN1</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>4D9033</t>
+          <t>4D9032</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO N 4</t>
+          <t>CUOTA SINDICATO N 1</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -54273,7 +54273,7 @@
         </is>
       </c>
       <c r="E388" s="3" t="n">
-        <v>9033</v>
+        <v>9032</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>3174 - Cuota sindical 4</t>
+          <t>3171 - Cuota sindical 1</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -54394,17 +54394,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>cuotaSindicatoN3</t>
+          <t>descuentasil</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>4D9034</t>
+          <t>4D9033</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO N 3</t>
+          <t>Descuenta Subsidio Incapacidad Laboral</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -54413,7 +54413,7 @@
         </is>
       </c>
       <c r="E389" s="3" t="n">
-        <v>9034</v>
+        <v>9033</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -54427,12 +54427,12 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>3173 - Cuota sindical 3</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
@@ -54457,12 +54457,12 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P389" t="inlineStr">
@@ -54472,7 +54472,7 @@
       </c>
       <c r="Q389" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R389" t="inlineStr">
@@ -54534,17 +54534,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>cuotaSindicatoN5</t>
+          <t>cuotaSindicatoN4</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>4D9035</t>
+          <t>4D9033</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO N 5</t>
+          <t>CUOTA SINDICATO N 4</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -54553,7 +54553,7 @@
         </is>
       </c>
       <c r="E390" s="3" t="n">
-        <v>9035</v>
+        <v>9033</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>3175 - Cuota sindical 5</t>
+          <t>3174 - Cuota sindical 4</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -54674,17 +54674,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>cuotaSindicatoN7</t>
+          <t>cuotaSindicatoN3</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>4D9036</t>
+          <t>4D9034</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO N 7</t>
+          <t>CUOTA SINDICATO N 3</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -54693,7 +54693,7 @@
         </is>
       </c>
       <c r="E391" s="3" t="n">
-        <v>9036</v>
+        <v>9034</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>3177 - Cuota sindical 7</t>
+          <t>3173 - Cuota sindical 3</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
@@ -54814,17 +54814,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>deportivoFinesco</t>
+          <t>cuotaSindicatoN5</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>4D9037</t>
+          <t>4D9035</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>DEPORTIVO FINESCO</t>
+          <t>CUOTA SINDICATO N 5</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -54833,7 +54833,7 @@
         </is>
       </c>
       <c r="E392" s="3" t="n">
-        <v>9037</v>
+        <v>9035</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3175 - Cuota sindical 5</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
@@ -54954,17 +54954,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>cuotaIncorporSi3IT98</t>
+          <t>cuotaSindicatoN7</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>4D9038</t>
+          <t>4D9036</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>CUOTA INCORPOR SINDICATO 6</t>
+          <t>CUOTA SINDICATO N 7</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -54973,7 +54973,7 @@
         </is>
       </c>
       <c r="E393" s="3" t="n">
-        <v>9038</v>
+        <v>9036</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3177 - Cuota sindical 7</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -55094,17 +55094,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>extensionSindicato1</t>
+          <t>deportivoFinesco</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>4D9039</t>
+          <t>4D9037</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>EXTENSION SINDICATO 1</t>
+          <t>DEPORTIVO FINESCO</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -55113,7 +55113,7 @@
         </is>
       </c>
       <c r="E394" s="3" t="n">
-        <v>9039</v>
+        <v>9037</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -55132,7 +55132,7 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>3171 - Cuota sindical 1</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
@@ -55234,17 +55234,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>cuotaIncorporSi3IT99</t>
+          <t>cuotaIncorporSi3IT98</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>4D9040</t>
+          <t>4D9038</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>CUOTA INCORPOR SINDICATO 7</t>
+          <t>CUOTA INCORPOR SINDICATO 6</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -55253,7 +55253,7 @@
         </is>
       </c>
       <c r="E395" s="3" t="n">
-        <v>9040</v>
+        <v>9038</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -55374,17 +55374,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>cuotaMortuoriaSJK2N3</t>
+          <t>extensionSindicato1</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>4D9041</t>
+          <t>4D9039</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>CUOTA MORTUORIA SINDICATO 3</t>
+          <t>EXTENSION SINDICATO 1</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -55393,7 +55393,7 @@
         </is>
       </c>
       <c r="E396" s="3" t="n">
-        <v>9041</v>
+        <v>9039</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>3173 - Cuota sindical 3</t>
+          <t>3171 - Cuota sindical 1</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
@@ -55514,17 +55514,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>comprasVariasSiZNVTD</t>
+          <t>cuotaIncorporSi3IT99</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>4D9042</t>
+          <t>4D9040</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>COMPRAS VARIAS SINDICATO N 2</t>
+          <t>CUOTA INCORPOR SINDICATO 7</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -55533,7 +55533,7 @@
         </is>
       </c>
       <c r="E397" s="3" t="n">
-        <v>9042</v>
+        <v>9040</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -55654,17 +55654,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>extensionSindicato5</t>
+          <t>cuotaMortuoriaSJK2N3</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>4D9043</t>
+          <t>4D9041</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>EXTENSION SINDICATO 5</t>
+          <t>CUOTA MORTUORIA SINDICATO 3</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -55673,7 +55673,7 @@
         </is>
       </c>
       <c r="E398" s="3" t="n">
-        <v>9043</v>
+        <v>9041</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>3175 - Cuota sindical 5</t>
+          <t>3173 - Cuota sindical 3</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
@@ -55794,17 +55794,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>extensionSindicato6</t>
+          <t>comprasVariasSiZNVTD</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>4D9044</t>
+          <t>4D9042</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>EXTENSION SINDICATO 6</t>
+          <t>COMPRAS VARIAS SINDICATO N 2</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -55813,7 +55813,7 @@
         </is>
       </c>
       <c r="E399" s="3" t="n">
-        <v>9044</v>
+        <v>9042</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>3176 - Cuota sindical 6</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -55934,17 +55934,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>extensionSindicato7</t>
+          <t>extensionSindicato5</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>4D9045</t>
+          <t>4D9043</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>EXTENSION SINDICATO 7</t>
+          <t>EXTENSION SINDICATO 5</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -55953,7 +55953,7 @@
         </is>
       </c>
       <c r="E400" s="3" t="n">
-        <v>9045</v>
+        <v>9043</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>3177 - Cuota sindical 7</t>
+          <t>3175 - Cuota sindical 5</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
@@ -56074,17 +56074,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>pagoDeReliquidacion</t>
+          <t>extensionSindicato6</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>4D9046</t>
+          <t>4D9044</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>PAGO DE RELIQUIDACION</t>
+          <t>EXTENSION SINDICATO 6</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -56093,7 +56093,7 @@
         </is>
       </c>
       <c r="E401" s="3" t="n">
-        <v>9046</v>
+        <v>9044</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -56112,7 +56112,7 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3176 - Cuota sindical 6</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
@@ -56214,17 +56214,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>reliquidacionEn0LVYK</t>
+          <t>extensionSindicato7</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>4D9047</t>
+          <t>4D9045</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>RELIQUIDACION EN CUENTA CTE</t>
+          <t>EXTENSION SINDICATO 7</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -56233,7 +56233,7 @@
         </is>
       </c>
       <c r="E402" s="3" t="n">
-        <v>9047</v>
+        <v>9045</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3177 - Cuota sindical 7</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -56287,7 +56287,7 @@
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -56354,17 +56354,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>comprasVariasSiZNVTF</t>
+          <t>pagoDeReliquidacion</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>4D9048</t>
+          <t>4D9046</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>COMPRAS VARIAS SINDICATO N 4</t>
+          <t>PAGO DE RELIQUIDACION</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -56373,7 +56373,7 @@
         </is>
       </c>
       <c r="E403" s="3" t="n">
-        <v>9048</v>
+        <v>9046</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -56494,17 +56494,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>comprasVariasSiZNVTI</t>
+          <t>reliquidacionEn0LVYK</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>4D9049</t>
+          <t>4D9047</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>COMPRAS VARIAS SINDICATO N 7</t>
+          <t>RELIQUIDACION EN CUENTA CTE</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -56513,7 +56513,7 @@
         </is>
       </c>
       <c r="E404" s="3" t="n">
-        <v>9049</v>
+        <v>9047</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -56567,7 +56567,7 @@
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -56634,17 +56634,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>cuotaMortuoriaSJK2N5</t>
+          <t>comprasVariasSiZNVTF</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>4D9050</t>
+          <t>4D9048</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>CUOTA MORTUORIA SINDICATO 5</t>
+          <t>COMPRAS VARIAS SINDICATO N 4</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -56653,7 +56653,7 @@
         </is>
       </c>
       <c r="E405" s="3" t="n">
-        <v>9050</v>
+        <v>9048</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -56774,17 +56774,17 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>comprasVariasSiZNVTE</t>
+          <t>comprasVariasSiZNVTI</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>4D9051</t>
+          <t>4D9049</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>COMPRAS VARIAS SINDICATO N 3</t>
+          <t>COMPRAS VARIAS SINDICATO N 7</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -56793,7 +56793,7 @@
         </is>
       </c>
       <c r="E406" s="3" t="n">
-        <v>9051</v>
+        <v>9049</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -56914,17 +56914,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>cuotaPrestamoEscolar</t>
+          <t>cuotaMortuoriaSJK2N5</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>4D9052</t>
+          <t>4D9050</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>CUOTA PRESTAMO ESCOLAR</t>
+          <t>CUOTA MORTUORIA SINDICATO 5</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -56933,7 +56933,7 @@
         </is>
       </c>
       <c r="E407" s="3" t="n">
-        <v>9052</v>
+        <v>9050</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -57054,17 +57054,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>prestamoEscolar</t>
+          <t>comprasVariasSiZNVTE</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>4D9054</t>
+          <t>4D9051</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>PRESTAMO ESCOLAR</t>
+          <t>COMPRAS VARIAS SINDICATO N 3</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -57073,7 +57073,7 @@
         </is>
       </c>
       <c r="E408" s="3" t="n">
-        <v>9054</v>
+        <v>9051</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -57092,7 +57092,7 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -57194,17 +57194,17 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>prestamoAporteECGBGI</t>
+          <t>cuotaPrestamoEscolar</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>4D9055</t>
+          <t>4D9052</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>PRESTAMO APORTE EDUCACIONAL</t>
+          <t>CUOTA PRESTAMO ESCOLAR</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -57213,7 +57213,7 @@
         </is>
       </c>
       <c r="E409" s="3" t="n">
-        <v>9055</v>
+        <v>9052</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -57334,17 +57334,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>prestamoAsignacOWVL9</t>
+          <t>prestamoEscolar</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>4D9056</t>
+          <t>4D9054</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>PRESTAMO ASIGNACION POR EDUCACION</t>
+          <t>PRESTAMO ESCOLAR</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -57353,7 +57353,7 @@
         </is>
       </c>
       <c r="E410" s="3" t="n">
-        <v>9056</v>
+        <v>9054</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -57474,17 +57474,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>extensionSindicato3</t>
+          <t>prestamoAporteECGBGI</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>4D9057</t>
+          <t>4D9055</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>EXTENSION SINDICATO 3</t>
+          <t>PRESTAMO APORTE EDUCACIONAL</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -57493,7 +57493,7 @@
         </is>
       </c>
       <c r="E411" s="3" t="n">
-        <v>9057</v>
+        <v>9055</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>3173 - Cuota sindical 3</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -57614,17 +57614,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>extensionSindicato4</t>
+          <t>prestamoAsignacOWVL9</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>4D9058</t>
+          <t>4D9056</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>EXTENSION SINDICATO 4</t>
+          <t>PRESTAMO ASIGNACION POR EDUCACION</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -57633,7 +57633,7 @@
         </is>
       </c>
       <c r="E412" s="3" t="n">
-        <v>9058</v>
+        <v>9056</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -57652,7 +57652,7 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>3174 - Cuota sindical 4</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -57754,17 +57754,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>anticipoBonoComVKMU4</t>
+          <t>extensionSindicato3</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>4D9059</t>
+          <t>4D9057</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>ANTICIPO BONO COMPENSACION VARIABLE</t>
+          <t>EXTENSION SINDICATO 3</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -57773,7 +57773,7 @@
         </is>
       </c>
       <c r="E413" s="3" t="n">
-        <v>9059</v>
+        <v>9057</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3173 - Cuota sindical 3</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -57894,17 +57894,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>prestamosEstudiS2QIZ</t>
+          <t>extensionSindicato4</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>4D9060</t>
+          <t>4D9058</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>PRESTAMOS ESTUDIOS SUPERIORES</t>
+          <t>EXTENSION SINDICATO 4</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -57913,7 +57913,7 @@
         </is>
       </c>
       <c r="E414" s="3" t="n">
-        <v>9060</v>
+        <v>9058</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -57932,7 +57932,7 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3174 - Cuota sindical 4</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -58034,17 +58034,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>descuentoExcesoWKU0Z</t>
+          <t>anticipoBonoComVKMU4</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>4D9061</t>
+          <t>4D9059</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>DESCUENTO EXCESO MAYO 2024</t>
+          <t>ANTICIPO BONO COMPENSACION VARIABLE</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -58053,7 +58053,7 @@
         </is>
       </c>
       <c r="E415" s="3" t="n">
-        <v>9061</v>
+        <v>9059</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -58174,17 +58174,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ahorroSocioASin3M6E0</t>
+          <t>prestamosEstudiS2QIZ</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>4D9062</t>
+          <t>4D9060</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>AHORRO SOCIO A SINDICATO 3</t>
+          <t>PRESTAMOS ESTUDIOS SUPERIORES</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -58193,7 +58193,7 @@
         </is>
       </c>
       <c r="E416" s="3" t="n">
-        <v>9062</v>
+        <v>9060</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -58212,7 +58212,7 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -58314,17 +58314,17 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>anticipoBonificL8YXT</t>
+          <t>descuentoExcesoWKU0Z</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>4D9063</t>
+          <t>4D9061</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>ANTICIPO BONIFICACION FERIADO</t>
+          <t>DESCUENTO EXCESO MAYO 2024</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -58333,7 +58333,7 @@
         </is>
       </c>
       <c r="E417" s="3" t="n">
-        <v>9063</v>
+        <v>9061</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -58454,17 +58454,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>descuentoCasinoONZYE</t>
+          <t>ahorroSocioASin3M6E0</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>4D9064</t>
+          <t>4D9062</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>DESCUENTO CASINO ANTOFAGASTA</t>
+          <t>AHORRO SOCIO A SINDICATO 3</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -58473,7 +58473,7 @@
         </is>
       </c>
       <c r="E418" s="3" t="n">
-        <v>9064</v>
+        <v>9062</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -58594,17 +58594,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>descuentoCasinoG4IR1</t>
+          <t>anticipoBonificL8YXT</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>4D9065</t>
+          <t>4D9063</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>DESCUENTO CASINO LA NEGRA</t>
+          <t>ANTICIPO BONIFICACION FERIADO</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -58613,7 +58613,7 @@
         </is>
       </c>
       <c r="E419" s="3" t="n">
-        <v>9065</v>
+        <v>9063</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -58632,7 +58632,7 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
@@ -58734,17 +58734,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>descuentoCasino2C43O</t>
+          <t>descuentoCasinoONZYE</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>4D9066</t>
+          <t>4D9064</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>DESCUENTO CASINO CAPACITACION</t>
+          <t>DESCUENTO CASINO ANTOFAGASTA</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -58753,7 +58753,7 @@
         </is>
       </c>
       <c r="E420" s="3" t="n">
-        <v>9066</v>
+        <v>9064</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -58874,17 +58874,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>descuentoCasinoFHYAG</t>
+          <t>descuentoCasinoG4IR1</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>4D9067</t>
+          <t>4D9065</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>DESCUENTO CASINO SUC SANTIAGO</t>
+          <t>DESCUENTO CASINO LA NEGRA</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -58893,7 +58893,7 @@
         </is>
       </c>
       <c r="E421" s="3" t="n">
-        <v>9067</v>
+        <v>9065</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -59014,17 +59014,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>descuentoCasinoPJF2B</t>
+          <t>descuentoCasino2C43O</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>4D9068</t>
+          <t>4D9066</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>DESCUENTO CASINO HUECHURABA</t>
+          <t>DESCUENTO CASINO CAPACITACION</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -59033,7 +59033,7 @@
         </is>
       </c>
       <c r="E422" s="3" t="n">
-        <v>9068</v>
+        <v>9066</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -59154,17 +59154,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>descuentosBenefWNTR4</t>
+          <t>descuentoCasinoFHYAG</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>4D9069</t>
+          <t>4D9067</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>DESCUENTOS BENEFICIO LIC MEDICA</t>
+          <t>DESCUENTO CASINO SUC SANTIAGO</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -59173,7 +59173,7 @@
         </is>
       </c>
       <c r="E423" s="3" t="n">
-        <v>9069</v>
+        <v>9067</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -59294,17 +59294,17 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>diferenciaDeIsapre</t>
+          <t>descuentoCasinoPJF2B</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>4D9072</t>
+          <t>4D9068</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>DIFERENCIA DE ISAPRE</t>
+          <t>DESCUENTO CASINO HUECHURABA</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -59313,7 +59313,7 @@
         </is>
       </c>
       <c r="E424" s="3" t="n">
-        <v>9072</v>
+        <v>9068</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -59434,17 +59434,17 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>consorcioNacionI3QVX</t>
+          <t>descuentosBenefWNTR4</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>4D9073</t>
+          <t>4D9069</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>CONSORCIO NACIONAL DE SEGUROS</t>
+          <t>DESCUENTOS BENEFICIO LIC MEDICA</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -59453,7 +59453,7 @@
         </is>
       </c>
       <c r="E425" s="3" t="n">
-        <v>9073</v>
+        <v>9069</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -59574,17 +59574,17 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>bonoPermanenciaXSE75</t>
+          <t>diferenciaDeIsapre</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>4D9074</t>
+          <t>4D9072</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>BONO PERMANENCIA DESCUENTO</t>
+          <t>DIFERENCIA DE ISAPRE</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -59593,7 +59593,7 @@
         </is>
       </c>
       <c r="E426" s="3" t="n">
-        <v>9074</v>
+        <v>9072</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -59714,17 +59714,17 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>apvIndivEmpleadYM9LL</t>
+          <t>consorcioNacionI3QVX</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>4D9079</t>
+          <t>4D9073</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>APV INDIV EMPLEADO SIN REBAJA TRIB UF</t>
+          <t>CONSORCIO NACIONAL DE SEGUROS</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -59733,7 +59733,7 @@
         </is>
       </c>
       <c r="E427" s="3" t="n">
-        <v>9079</v>
+        <v>9073</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>3155 - Cotización APVi Mod A</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -59854,17 +59854,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>descuentoPorComHV68N</t>
+          <t>bonoPermanenciaXSE75</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>4D9082</t>
+          <t>4D9074</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>DESCUENTO POR COMPRA ESPP</t>
+          <t>BONO PERMANENCIA DESCUENTO</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -59873,7 +59873,7 @@
         </is>
       </c>
       <c r="E428" s="3" t="n">
-        <v>9082</v>
+        <v>9074</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -59994,17 +59994,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>descuentosVarios</t>
+          <t>apvIndivEmpleadYM9LL</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>4D9099</t>
+          <t>4D9079</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Descuentos Varios</t>
+          <t>APV INDIV EMPLEADO SIN REBAJA TRIB UF</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -60013,7 +60013,7 @@
         </is>
       </c>
       <c r="E429" s="3" t="n">
-        <v>9099</v>
+        <v>9079</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -60027,12 +60027,12 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>3185 - Otros descuentos</t>
+          <t>3155 - Cotización APVi Mod A</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -60057,12 +60057,12 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P429" t="inlineStr">
@@ -60072,7 +60072,7 @@
       </c>
       <c r="Q429" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R429" t="inlineStr">
@@ -60134,17 +60134,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>retencionJudicial</t>
+          <t>descuentoPorComHV68N</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>4D9100</t>
+          <t>4D9082</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Retencion Judicial</t>
+          <t>DESCUENTO POR COMPRA ESPP</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -60153,7 +60153,7 @@
         </is>
       </c>
       <c r="E430" s="3" t="n">
-        <v>9100</v>
+        <v>9082</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -60167,12 +60167,12 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>3186 - Pensiones de alimentos</t>
+          <t>3183 - Otros descuentos autorizados y solicitados por el trabajador</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -60197,12 +60197,12 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P430" t="inlineStr">
@@ -60212,7 +60212,7 @@
       </c>
       <c r="Q430" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R430" t="inlineStr">
@@ -60274,17 +60274,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>anticipoBonoProX57J9</t>
+          <t>descuentosVarios</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>4D9242</t>
+          <t>4D9099</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>ANTICIPO BONO PRODUCTIVIDAD</t>
+          <t>Descuentos Varios</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -60293,7 +60293,7 @@
         </is>
       </c>
       <c r="E431" s="3" t="n">
-        <v>9242</v>
+        <v>9099</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -60307,12 +60307,12 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3185 - Otros descuentos</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
@@ -60337,12 +60337,12 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P431" t="inlineStr">
@@ -60352,7 +60352,7 @@
       </c>
       <c r="Q431" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R431" t="inlineStr">
@@ -60414,17 +60414,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>cuotaSindicatoNMN4QC</t>
+          <t>retencionJudicial</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>4D9299</t>
+          <t>4D9100</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>CUOTA SINDICATO N 2 RENTAL</t>
+          <t>Retencion Judicial</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -60433,7 +60433,7 @@
         </is>
       </c>
       <c r="E432" s="3" t="n">
-        <v>9299</v>
+        <v>9100</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -60447,12 +60447,12 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>3172 - Cuota sindical 2</t>
+          <t>3186 - Pensiones de alimentos</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -60477,12 +60477,12 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P432" t="inlineStr">
@@ -60492,7 +60492,7 @@
       </c>
       <c r="Q432" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R432" t="inlineStr">
@@ -60554,17 +60554,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>anticipoTransfer</t>
+          <t>anticipoBonoProX57J9</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>4D9980</t>
+          <t>4D9242</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Anticipo pagado por Transfer</t>
+          <t>ANTICIPO BONO PRODUCTIVIDAD</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -60573,7 +60573,7 @@
         </is>
       </c>
       <c r="E433" s="3" t="n">
-        <v>9980</v>
+        <v>9242</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -60587,7 +60587,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -60617,12 +60617,12 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P433" t="inlineStr">
@@ -60632,7 +60632,7 @@
       </c>
       <c r="Q433" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R433" t="inlineStr">
@@ -60694,17 +60694,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>anticipoTransferliq</t>
+          <t>cuotaSindicatoNMN4QC</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>4D9981</t>
+          <t>4D9299</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Transfer (no descuenta)</t>
+          <t>CUOTA SINDICATO N 2 RENTAL</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -60713,7 +60713,7 @@
         </is>
       </c>
       <c r="E434" s="3" t="n">
-        <v>9981</v>
+        <v>9299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -60727,12 +60727,12 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>3172 - Cuota sindical 2</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -60757,12 +60757,12 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P434" t="inlineStr">
@@ -60772,7 +60772,7 @@
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -60834,17 +60834,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>totalHonorarios</t>
+          <t>anticipoTransfer</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>4D9990</t>
+          <t>4D9980</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Honorario liquido</t>
+          <t>Anticipo pagado por Transfer</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -60853,7 +60853,7 @@
         </is>
       </c>
       <c r="E435" s="3" t="n">
-        <v>9990</v>
+        <v>9980</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -60868,6 +60868,11 @@
       <c r="H435" t="inlineStr">
         <is>
           <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -60969,17 +60974,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>totalesEmpl</t>
+          <t>anticipoTransferliq</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>4D9990</t>
+          <t>4D9981</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Sueldo liquido</t>
+          <t>Transfer (no descuenta)</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -60988,7 +60993,7 @@
         </is>
       </c>
       <c r="E436" s="3" t="n">
-        <v>9990</v>
+        <v>9981</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -61007,7 +61012,7 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>5501 - Total líquido</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -61022,7 +61027,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -61109,17 +61114,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>desc_antic_quincenal</t>
+          <t>totalesEmpl</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>4D9991</t>
+          <t>4D9990</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>DESCUENTO ANTICIPO QUINCENAL</t>
+          <t>Sueldo liquido</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -61128,7 +61133,7 @@
         </is>
       </c>
       <c r="E437" s="3" t="n">
-        <v>9991</v>
+        <v>9990</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -61142,12 +61147,12 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>3188 - Descuentos por anticipos y préstamos</t>
+          <t>5501 - Total líquido</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -61162,7 +61167,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -61249,17 +61254,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>extensionSindicato2</t>
+          <t>totalHonorarios</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>4D9992</t>
+          <t>4D9990</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>EXTENSION SINDICATO 2 RENTAL</t>
+          <t>Honorario liquido</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -61268,7 +61273,7 @@
         </is>
       </c>
       <c r="E438" s="3" t="n">
-        <v>9992</v>
+        <v>9990</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -61282,12 +61287,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>3172 - Cuota sindical 2</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -61389,17 +61389,17 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>aporteBienestar</t>
+          <t>desc_antic_quincenal</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>4D9993</t>
+          <t>4D9991</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>APORTE BIENESTAR</t>
+          <t>DESCUENTO ANTICIPO QUINCENAL</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -61408,7 +61408,7 @@
         </is>
       </c>
       <c r="E439" s="3" t="n">
-        <v>9993</v>
+        <v>9991</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -61427,7 +61427,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>2123 - Otras remuneraciones superiores a un mes</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -61452,22 +61452,22 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R439" t="inlineStr">
@@ -61529,26 +61529,26 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>trabajoPesa</t>
+          <t>extensionSindicato2</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>5A0150</t>
+          <t>4D9992</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Trabajo Pesado</t>
+          <t>EXTENSION SINDICATO 2 RENTAL</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Aporte Empleador</t>
+          <t>Descuento</t>
         </is>
       </c>
       <c r="E440" s="3" t="n">
-        <v>150</v>
+        <v>9992</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -61562,12 +61562,12 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>4154 - Aporte adicional trabajo pesado - empleador</t>
+          <t>3172 - Cuota sindical 2</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -61592,12 +61592,12 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P440" t="inlineStr">
@@ -61607,7 +61607,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R440" t="inlineStr">
@@ -61669,26 +61669,26 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>reliquidaTrabPesa</t>
+          <t>aporteBienestar</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>5A0151</t>
+          <t>4D9993</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Trabajo pesado Reliq anteriores</t>
+          <t>APORTE BIENESTAR</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Aporte Empleador</t>
+          <t>Descuento</t>
         </is>
       </c>
       <c r="E441" s="3" t="n">
-        <v>151</v>
+        <v>9993</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -61702,12 +61702,12 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>4154 - Aporte adicional trabajo pesado - empleador</t>
+          <t>2123 - Otras remuneraciones superiores a un mes</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -61742,7 +61742,7 @@
       </c>
       <c r="P441" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q441" t="inlineStr">
@@ -61809,26 +61809,26 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>apvcAporte</t>
+          <t>prestamo</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>5A0201</t>
+          <t>4D9994</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>APVC Aporte Empleador</t>
+          <t>PRESTAMO</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Aporte Empleador</t>
+          <t>Descuento</t>
         </is>
       </c>
       <c r="E442" s="3" t="n">
-        <v>201</v>
+        <v>9994</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -61842,12 +61842,12 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>4157 - APVC - Aporte Empleador</t>
+          <t>3188 - Descuentos por anticipos y préstamos</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -61882,7 +61882,7 @@
       </c>
       <c r="P442" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q442" t="inlineStr">
@@ -61949,26 +61949,26 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ley21227_afp</t>
+          <t>cuotaMortuoriaSJK2N6</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>5A0261</t>
+          <t>4D9995</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Aporte Ley 21227 AFP</t>
+          <t>CUOTA MORTUORIA SINDICATO 6</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Aporte Empleador</t>
+          <t>Descuento</t>
         </is>
       </c>
       <c r="E443" s="3" t="n">
-        <v>261</v>
+        <v>9995</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -61982,7 +61982,12 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>ine_aposeg</t>
+          <t>ine_noAplica</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>3185 - Otros descuentos</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -62017,7 +62022,7 @@
       </c>
       <c r="P443" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q443" t="inlineStr">
@@ -62084,17 +62089,17 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ley21227_sis</t>
+          <t>trabajoPesa</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>5A0262</t>
+          <t>5A0150</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Aporte Ley 21227 SIS</t>
+          <t>Trabajo Pesado</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -62103,7 +62108,7 @@
         </is>
       </c>
       <c r="E444" s="3" t="n">
-        <v>262</v>
+        <v>150</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -62117,12 +62122,12 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>ine_aposeg</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>4155 - Aporte empleador seguro invalidez y sobrevivencia</t>
+          <t>4154 - Aporte adicional trabajo pesado - empleador</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
@@ -62224,17 +62229,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>ley21227_mutual</t>
+          <t>reliquidaTrabPesa</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>5A0263</t>
+          <t>5A0151</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Aporte Ley 21227 Mutual</t>
+          <t>Trabajo pesado Reliq anteriores</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -62243,7 +62248,7 @@
         </is>
       </c>
       <c r="E445" s="3" t="n">
-        <v>263</v>
+        <v>151</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -62257,12 +62262,12 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>ine_aposeg</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>4152 - Aporte empleador seguro accidentes del trabajo y Ley SANNA</t>
+          <t>4154 - Aporte adicional trabajo pesado - empleador</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -62364,17 +62369,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ley21227_salud</t>
+          <t>apvcAporte</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>5A0264</t>
+          <t>5A0201</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Aporte Ley 21227 Salud</t>
+          <t>APVC Aporte Empleador</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -62383,7 +62388,7 @@
         </is>
       </c>
       <c r="E446" s="3" t="n">
-        <v>264</v>
+        <v>201</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -62397,7 +62402,12 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>ine_aposeg</t>
+          <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>4157 - APVC - Aporte Empleador</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -62499,17 +62509,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>ley21227_afcempleado</t>
+          <t>ley21227_afp</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>5A0265</t>
+          <t>5A0261</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Aporte Ley 21227 AFC Empleado</t>
+          <t>Aporte Ley 21227 AFP</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -62518,7 +62528,7 @@
         </is>
       </c>
       <c r="E447" s="3" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -62533,11 +62543,6 @@
       <c r="H447" t="inlineStr">
         <is>
           <t>ine_aposeg</t>
-        </is>
-      </c>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -62639,17 +62644,17 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>ley21227_afcci</t>
+          <t>ley21227_sis</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>5A0266</t>
+          <t>5A0262</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Aporte Ley 21227 AFC Cuenta Individual</t>
+          <t>Aporte Ley 21227 SIS</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -62658,7 +62663,7 @@
         </is>
       </c>
       <c r="E448" s="3" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -62677,7 +62682,7 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>4155 - Aporte empleador seguro invalidez y sobrevivencia</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -62779,17 +62784,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ley21227_afcsol</t>
+          <t>ley21227_mutual</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>5A0267</t>
+          <t>5A0263</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Aporte Ley 21227 AFC Cuenta solidaria</t>
+          <t>Aporte Ley 21227 Mutual</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -62798,7 +62803,7 @@
         </is>
       </c>
       <c r="E449" s="3" t="n">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -62817,7 +62822,7 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>4152 - Aporte empleador seguro accidentes del trabajo y Ley SANNA</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -62919,17 +62924,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>ley21227_cajaco</t>
+          <t>ley21227_salud</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>5A0268</t>
+          <t>5A0264</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Aporte Ley 21227 Caja Compensacion</t>
+          <t>Aporte Ley 21227 Salud</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -62938,7 +62943,7 @@
         </is>
       </c>
       <c r="E450" s="3" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -63054,17 +63059,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>cajaComp</t>
+          <t>ley21227_afcempleado</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>5A0300</t>
+          <t>5A0265</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Aporte a CCAF</t>
+          <t>Aporte Ley 21227 AFC Empleado</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -63073,7 +63078,7 @@
         </is>
       </c>
       <c r="E451" s="3" t="n">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -63087,7 +63092,12 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_aposeg</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -63189,17 +63199,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>reliquidaCcaf</t>
+          <t>ley21227_afcci</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>5A0301</t>
+          <t>5A0266</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>CCAF Reliq meses anteriores</t>
+          <t>Aporte Ley 21227 AFC Cuenta Individual</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -63208,7 +63218,7 @@
         </is>
       </c>
       <c r="E452" s="3" t="n">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -63222,7 +63232,12 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_aposeg</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -63324,17 +63339,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>mutual</t>
+          <t>ley21227_afcsol</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>5A0400</t>
+          <t>5A0267</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Mutual</t>
+          <t>Aporte Ley 21227 AFC Cuenta solidaria</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -63343,7 +63358,7 @@
         </is>
       </c>
       <c r="E453" s="3" t="n">
-        <v>400</v>
+        <v>267</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -63357,12 +63372,12 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_aposeg</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>4152 - Aporte empleador seguro accidentes del trabajo y Ley SANNA</t>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -63464,17 +63479,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>reliquidaMutual</t>
+          <t>ley21227_cajaco</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>5A0401</t>
+          <t>5A0268</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>MUTUAL Reliq meses anteriores</t>
+          <t>Aporte Ley 21227 Caja Compensacion</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -63483,7 +63498,7 @@
         </is>
       </c>
       <c r="E454" s="3" t="n">
-        <v>401</v>
+        <v>268</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -63497,12 +63512,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
-        </is>
-      </c>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>4152 - Aporte empleador seguro accidentes del trabajo y Ley SANNA</t>
+          <t>ine_aposeg</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -63604,17 +63614,17 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>sis</t>
+          <t>cajaComp</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>5A0500</t>
+          <t>5A0300</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Seguro Invalidez y Sobrevivencia</t>
+          <t>Aporte a CCAF</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -63623,7 +63633,7 @@
         </is>
       </c>
       <c r="E455" s="3" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -63638,11 +63648,6 @@
       <c r="H455" t="inlineStr">
         <is>
           <t>Sin Definir</t>
-        </is>
-      </c>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>4155 - Aporte empleador seguro invalidez y sobrevivencia</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -63744,17 +63749,17 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>reliquidaSis</t>
+          <t>reliquidaCcaf</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>5A0501</t>
+          <t>5A0301</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>SIS Reliq meses anteriores</t>
+          <t>CCAF Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -63763,7 +63768,7 @@
         </is>
       </c>
       <c r="E456" s="3" t="n">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -63778,11 +63783,6 @@
       <c r="H456" t="inlineStr">
         <is>
           <t>Sin Definir</t>
-        </is>
-      </c>
-      <c r="I456" t="inlineStr">
-        <is>
-          <t>4155 - Aporte empleador seguro invalidez y sobrevivencia</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -63884,17 +63884,17 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>cesAporteCi</t>
+          <t>mutual</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>5A0520</t>
+          <t>5A0400</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Seguro de Cesantia CI</t>
+          <t>Mutual</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -63903,7 +63903,7 @@
         </is>
       </c>
       <c r="E457" s="3" t="n">
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -63922,7 +63922,7 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>4152 - Aporte empleador seguro accidentes del trabajo y Ley SANNA</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -64024,17 +64024,17 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>reliquidaCesCi</t>
+          <t>reliquidaMutual</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>5A0521</t>
+          <t>5A0401</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>CESANTIA CI Reliq meses anteriores</t>
+          <t>MUTUAL Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -64043,7 +64043,7 @@
         </is>
       </c>
       <c r="E458" s="3" t="n">
-        <v>521</v>
+        <v>401</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>4152 - Aporte empleador seguro accidentes del trabajo y Ley SANNA</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -64164,17 +64164,17 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>cesAporteSol</t>
+          <t>sis</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>5A0530</t>
+          <t>5A0500</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Seguro de Cesantia Solidario</t>
+          <t>Seguro Invalidez y Sobrevivencia</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -64183,7 +64183,7 @@
         </is>
       </c>
       <c r="E459" s="3" t="n">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -64202,7 +64202,7 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>4155 - Aporte empleador seguro invalidez y sobrevivencia</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -64304,17 +64304,17 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>reliquidaCesSol</t>
+          <t>reliquidaSis</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>5A0531</t>
+          <t>5A0501</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>CESANTIA SOL Reliq meses anteriores</t>
+          <t>SIS Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -64323,7 +64323,7 @@
         </is>
       </c>
       <c r="E460" s="3" t="n">
-        <v>531</v>
+        <v>501</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>4155 - Aporte empleador seguro invalidez y sobrevivencia</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -64444,17 +64444,17 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>aporteAFPemp</t>
+          <t>cesAporteCi</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>5A0540</t>
+          <t>5A0520</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Aporte AFP Empleador</t>
+          <t>Seguro de Cesantia CI</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -64463,7 +64463,7 @@
         </is>
       </c>
       <c r="E461" s="3" t="n">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -64478,6 +64478,11 @@
       <c r="H461" t="inlineStr">
         <is>
           <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -64579,17 +64584,17 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>reliquidaAporteAFP</t>
+          <t>reliquidaCesCi</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>5A0541</t>
+          <t>5A0521</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Aporte AFP Empleador Reliq meses anteriores</t>
+          <t>CESANTIA CI Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -64598,7 +64603,7 @@
         </is>
       </c>
       <c r="E462" s="3" t="n">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -64613,6 +64618,11 @@
       <c r="H462" t="inlineStr">
         <is>
           <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -64714,17 +64724,17 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>aporteFAPPCEV</t>
+          <t>cesAporteSol</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>5A0550</t>
+          <t>5A0530</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Aporte FAPP Compensación Expectativa de Vida</t>
+          <t>Seguro de Cesantia Solidario</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -64733,7 +64743,7 @@
         </is>
       </c>
       <c r="E463" s="3" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -64748,6 +64758,11 @@
       <c r="H463" t="inlineStr">
         <is>
           <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -64849,17 +64864,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>reliquidaAporteCEV</t>
+          <t>reliquidaCesSol</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>5A0551</t>
+          <t>5A0531</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Aporte FAPP CEV Reliq meses anteriores</t>
+          <t>CESANTIA SOL Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -64868,7 +64883,7 @@
         </is>
       </c>
       <c r="E464" s="3" t="n">
-        <v>551</v>
+        <v>531</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -64883,6 +64898,11 @@
       <c r="H464" t="inlineStr">
         <is>
           <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -64984,17 +65004,17 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>aporteFAPPBAC</t>
+          <t>aporteAFPemp</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>5A0560</t>
+          <t>5A0540</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Aporte FAPP Beneficio años cotizados</t>
+          <t>Aporte AFP Empleador</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -65003,7 +65023,7 @@
         </is>
       </c>
       <c r="E465" s="3" t="n">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -65119,17 +65139,17 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>reliquidaAporteBAC</t>
+          <t>reliquidaAporteAFP</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>5A0561</t>
+          <t>5A0541</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Aporte FAPP BAC Reliq meses anteriores</t>
+          <t>Aporte AFP Empleador Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -65138,7 +65158,7 @@
         </is>
       </c>
       <c r="E466" s="3" t="n">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -65254,17 +65274,17 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>aportesegurocovid</t>
+          <t>aporteFAPPCEV</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>5A0563</t>
+          <t>5A0550</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Aporte por Seguro Covid</t>
+          <t>Aporte FAPP Compensación Expectativa de Vida</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -65273,7 +65293,7 @@
         </is>
       </c>
       <c r="E467" s="3" t="n">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -65389,17 +65409,17 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>segCesEmpleadorReliq</t>
+          <t>reliquidaAporteCEV</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>5A6452</t>
+          <t>5A0551</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>SEG CES EMPLEADOR RELIQ</t>
+          <t>Aporte FAPP CEV Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -65408,7 +65428,7 @@
         </is>
       </c>
       <c r="E468" s="3" t="n">
-        <v>6452</v>
+        <v>551</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -65422,12 +65442,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
-        </is>
-      </c>
-      <c r="I468" t="inlineStr">
-        <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -65529,17 +65544,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>aporteEmpleadorMOLDR</t>
+          <t>aporteFAPPBAC</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>5A9226</t>
+          <t>5A0560</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>APORTE EMPLEADOR SEG CESANTIA</t>
+          <t>Aporte FAPP Beneficio años cotizados</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -65548,7 +65563,7 @@
         </is>
       </c>
       <c r="E469" s="3" t="n">
-        <v>9226</v>
+        <v>560</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -65562,12 +65577,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
-        </is>
-      </c>
-      <c r="I469" t="inlineStr">
-        <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -65669,17 +65679,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>aporteEmpleadorXTCD2</t>
+          <t>reliquidaAporteBAC</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>5A9227</t>
+          <t>5A0561</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>APORTE EMPLEADOR FONDO INDEMNI</t>
+          <t>Aporte FAPP BAC Reliq meses anteriores</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -65688,7 +65698,7 @@
         </is>
       </c>
       <c r="E470" s="3" t="n">
-        <v>9227</v>
+        <v>561</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -65702,12 +65712,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>ine_noAplica</t>
-        </is>
-      </c>
-      <c r="I470" t="inlineStr">
-        <is>
-          <t>4151 - AFC - Aporte empleador</t>
+          <t>Sin Definir</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -65809,26 +65814,26 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>subjoven</t>
+          <t>aportesegurocovid</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>8G0020</t>
+          <t>5A0563</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Subsidio trabajador joven</t>
+          <t>Aporte por Seguro Covid</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Valor Guardado</t>
+          <t>Aporte Empleador</t>
         </is>
       </c>
       <c r="E471" s="3" t="n">
-        <v>20</v>
+        <v>563</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -65852,7 +65857,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -65867,12 +65872,12 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P471" t="inlineStr">
@@ -65882,7 +65887,7 @@
       </c>
       <c r="Q471" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R471" t="inlineStr">
@@ -65944,26 +65949,26 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>provisionVacacionMes</t>
+          <t>segCesEmpleadorReliq</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>8G0301</t>
+          <t>5A6452</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Provision Vacaciones</t>
+          <t>SEG CES EMPLEADOR RELIQ</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Valor Guardado</t>
+          <t>Aporte Empleador</t>
         </is>
       </c>
       <c r="E472" s="3" t="n">
-        <v>301</v>
+        <v>6452</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -65977,7 +65982,12 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -66002,12 +66012,12 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P472" t="inlineStr">
@@ -66017,7 +66027,7 @@
       </c>
       <c r="Q472" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R472" t="inlineStr">
@@ -66079,26 +66089,26 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>provisionIasMes</t>
+          <t>aporteEmpleadorMOLDR</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>8G0302</t>
+          <t>5A9226</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Provision IAS</t>
+          <t>APORTE EMPLEADOR SEG CESANTIA</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Valor Guardado</t>
+          <t>Aporte Empleador</t>
         </is>
       </c>
       <c r="E473" s="3" t="n">
-        <v>302</v>
+        <v>9226</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -66112,7 +66122,12 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
@@ -66137,12 +66152,12 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P473" t="inlineStr">
@@ -66152,7 +66167,7 @@
       </c>
       <c r="Q473" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R473" t="inlineStr">
@@ -66162,7 +66177,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="T473" t="inlineStr">
@@ -66214,26 +66229,26 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>provisionVacAumento</t>
+          <t>aporteEmpleadorXTCD2</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>8G0303</t>
+          <t>5A9227</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Provision Vacaciones Aumento mes</t>
+          <t>APORTE EMPLEADOR FONDO INDEMNI</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Valor Guardado</t>
+          <t>Aporte Empleador</t>
         </is>
       </c>
       <c r="E474" s="3" t="n">
-        <v>303</v>
+        <v>9227</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -66247,7 +66262,12 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Sin Definir</t>
+          <t>ine_noAplica</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>4151 - AFC - Aporte empleador</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -66272,12 +66292,12 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P474" t="inlineStr">
@@ -66287,7 +66307,7 @@
       </c>
       <c r="Q474" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R474" t="inlineStr">
@@ -66349,17 +66369,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>provisionVacDisminu</t>
+          <t>subjoven</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>8G0304</t>
+          <t>8G0020</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Provision Vacaciones Disminucion mes</t>
+          <t>Subsidio trabajador joven</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -66368,7 +66388,7 @@
         </is>
       </c>
       <c r="E475" s="3" t="n">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -66392,7 +66412,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -66484,17 +66504,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>provisionVacDevengo</t>
+          <t>provisionVacacionMes</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>8G0305</t>
+          <t>8G0301</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Provision Vacaciones Devengo del mes</t>
+          <t>Provision Vacaciones</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -66503,7 +66523,7 @@
         </is>
       </c>
       <c r="E476" s="3" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -66619,17 +66639,17 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>provisionVacConsumo</t>
+          <t>provisionIasMes</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>8G0306</t>
+          <t>8G0302</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Provision Vacaciones Consumo del mes</t>
+          <t>Provision IAS</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -66638,7 +66658,7 @@
         </is>
       </c>
       <c r="E477" s="3" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -66702,7 +66722,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T477" t="inlineStr">
@@ -66754,17 +66774,17 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>provisionVacDifAju</t>
+          <t>provisionVacAumento</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>8G0395</t>
+          <t>8G0303</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Provision Vacaciones Diferencia ajuste</t>
+          <t>Provision Vacaciones Aumento mes</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -66773,7 +66793,7 @@
         </is>
       </c>
       <c r="E478" s="3" t="n">
-        <v>395</v>
+        <v>303</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -66889,17 +66909,17 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>provisionVacSaldo</t>
+          <t>provisionVacDisminu</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>8G0396</t>
+          <t>8G0304</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Provision Vacaciones Saldo de provisión</t>
+          <t>Provision Vacaciones Disminucion mes</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -66908,7 +66928,7 @@
         </is>
       </c>
       <c r="E479" s="3" t="n">
-        <v>396</v>
+        <v>304</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -67024,26 +67044,26 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>vacacionesNorm</t>
+          <t>provisionVacDevengo</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>9V1010</t>
+          <t>8G0305</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Vacaciones Normales</t>
+          <t>Provision Vacaciones Devengo del mes</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Valor Guardado</t>
         </is>
       </c>
       <c r="E480" s="3" t="n">
-        <v>1010</v>
+        <v>305</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -67067,7 +67087,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -67082,12 +67102,12 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P480" t="inlineStr">
@@ -67097,7 +67117,7 @@
       </c>
       <c r="Q480" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R480" t="inlineStr">
@@ -67159,133 +67179,673 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
+          <t>provisionVacConsumo</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>8G0306</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Provision Vacaciones Consumo del mes</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Valor Guardado</t>
+        </is>
+      </c>
+      <c r="E481" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Monto Fijo</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>provisionVacDifAju</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>8G0395</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Provision Vacaciones Diferencia ajuste</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Valor Guardado</t>
+        </is>
+      </c>
+      <c r="E482" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Monto Fijo</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>provisionVacSaldo</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>8G0396</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Provision Vacaciones Saldo de provisión</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Valor Guardado</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="n">
+        <v>396</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Monto Fijo</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X483" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>vacacionesNorm</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>9V1010</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Vacaciones Normales</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Vacaciones</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Monto Fijo</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Sin Definir</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X484" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
           <t>vacacionesProg</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B485" t="inlineStr">
         <is>
           <t>9V1020</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
+      <c r="C485" t="inlineStr">
         <is>
           <t>Vacaciones Progresivas</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr">
+      <c r="D485" t="inlineStr">
         <is>
           <t>Vacaciones</t>
         </is>
       </c>
-      <c r="E481" s="3" t="n">
+      <c r="E485" s="3" t="n">
         <v>1020</v>
       </c>
-      <c r="F481" t="inlineStr">
+      <c r="F485" t="inlineStr">
         <is>
           <t>Monto Fijo</t>
         </is>
       </c>
-      <c r="G481" t="inlineStr">
+      <c r="G485" t="inlineStr">
         <is>
           <t>Sin categoría</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr">
+      <c r="H485" t="inlineStr">
         <is>
           <t>Sin Definir</t>
         </is>
       </c>
-      <c r="J481" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="K481" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P481" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Q481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X481" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Y481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA481" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB481" t="inlineStr">
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB485" t="inlineStr">
         <is>
           <t>No</t>
         </is>
